--- a/05_xlsx_docx_pdf/distritos-ejemplo_v2.xlsx
+++ b/05_xlsx_docx_pdf/distritos-ejemplo_v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="52695" yWindow="3045" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distrito_población" sheetId="1" state="visible" r:id="rId1"/>
@@ -391,10 +391,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15.453125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="16.08984375" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -463,6 +463,16 @@
       </c>
       <c r="B6" t="n">
         <v>233808</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
